--- a/federated_learning_results.xlsx
+++ b/federated_learning_results.xlsx
@@ -492,28 +492,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>22.27</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>40.28</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>103.36</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>91.69</v>
       </c>
       <c r="J2" t="n">
-        <v>84.92</v>
+        <v>68.66</v>
       </c>
     </row>
     <row r="3">
@@ -528,28 +528,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>17.08</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>29.78</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>75.83</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>91.56999999999999</v>
+        <v>91.69</v>
       </c>
       <c r="J3" t="n">
-        <v>86.06999999999999</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="4">
@@ -564,28 +564,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>9.92</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>18.41</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>47.66</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>80.06999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="J4" t="n">
-        <v>86.78</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="5">
@@ -600,28 +600,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>11.88</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>20.12</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>64.48</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>89.56</v>
+        <v>90.69</v>
       </c>
       <c r="J5" t="n">
-        <v>86.31</v>
+        <v>68.61</v>
       </c>
     </row>
   </sheetData>
